--- a/카드_낱말_목록.xlsx
+++ b/카드_낱말_목록.xlsx
@@ -808,12 +808,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>박쥐 한 마리</t>
+          <t>야구방망이 한 개</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>박쥐 여러 마리</t>
+          <t>야구방망이 여러 개</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>박쥐 한 마리</t>
+          <t>야구방망이 한 개</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>박쥐 여러 마리</t>
+          <t>야구방망이 여러 개</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
